--- a/sources/devil_step3.xlsx
+++ b/sources/devil_step3.xlsx
@@ -690,6 +690,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>d45bec05-7204-4250-b59f-10fc5a9777d7</t>
@@ -727,6 +732,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>17795a91-f2dd-40be-9ae8-c1cac544dbd8</t>
@@ -762,6 +772,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6cb3e0a1-740e-4fe0-abcb-9e9234259fe0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3538,6 +3553,11 @@
       <c r="I68" t="inlineStr">
         <is>
           <t>hhhhmmLhmm</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>f5b8d288-963e-48b0-91a0-9547d3e2d9cf</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
